--- a/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tessa s'assoit près de maman. Elles ouvrent une boîte de cartes. Maman dit : on nomme un pays. Tessa lit le nom : le Portugal. Elle répète : le Portugal. Sur la carte, de l'eau bleue. Maman dit : ça, c'est un paysage. C'est la mer. Tessa dit : la mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
+          <t>Tessa s'assoit près de maman. Elles ouvrent une boîte de cartes. On nomme un pays. Tessa lit le nom : le Portugal. Elle répète : le Portugal. Sur la carte, de l'eau bleue. Ça, c'est un paysage. C'est la mer. La mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tessa s'assoit près de maman. Elles ouvrent une boîte de cartes.
+maman|On nomme un pays.
+narrateur|Tessa lit le nom : le Portugal. Elle répète : le Portugal. Sur la carte, de l'eau bleue.
+maman|Ça, c'est un paysage. C'est la mer.
+enfant-f|La mer. Autre carte : des sommets.
+narrateur|Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tessa nomme le Portugal. Elle nomme aussi quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tessa a dit le nom. Le Portugal. Elle a dit le paysage. La mer. La montagne aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Tessa range les cartes. Maman ferme la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Tessa nomme le Portugal. Elle nomme aussi quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Tessa a dit le nom. Le Portugal. Elle a dit le paysage. La mer. La montagne aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Tessa range les cartes. Maman ferme la boîte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tessa nomme le Portugal et la mer</t>
+          <t>La sardine de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut voir la mer du Portugal sur l'image de sardine pendant que ça sent la cuisine. Une goutte d'huile tache le coin. Elles essuient. Le bleu revient.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tessa s'assoit près de maman. Elles ouvrent une boîte de cartes. On nomme un pays. Tessa lit le nom : le Portugal. Elle répète : le Portugal. Sur la carte, de l'eau bleue. Ça, c'est un paysage. C'est la mer. La mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
+          <t>L'huile chaude sent le citron dans la cuisine. Une poêle fait un petit chant gras. La fenêtre est ouverte sur la cour. Une sardine dessinée attend près du pain. Chouchou vit ici, avec maman. Tu as vu la boîte, Chouchou ? Il y a un poisson. Une sardine. Dessinée, sur le Portugal. En ce moment, Chouchou prend la boîte. Le métal est froid, un peu huileux. Derrière le poisson, c'est bleu. C'est la mer du Portugal. Le Portugal. Et la mer. Un pays. Un paysage. Chouchou veut poser l'image près d'elle. Pour voir la mer, en mangeant. Tu la mets contre le sel ? Oui. La poêle crache une goutte. La goutte d'huile tombe sur le coin. Oh. Le bleu est taché ! On essuie tout de suite ? Oui, maman. Maman tend un torchon sec. Chouchou tamponne le coin, tout doux. L'huile fait un rond brillant. Ça part ? Encore un peu. Le torchon sent le citron, maintenant. Le rond devient plus pâle. La sardine est encore là. Et la mer, derrière ? Elle revient. Tu tamponnes bien. Une miette de pain roule près de la boîte. Chouchou la pousse du doigt.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tessa s'assoit près de maman. Elles ouvrent une boîte de cartes. Maman dit : on &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un pays. Tessa lit le nom : le Portugal. Elle répète : le Portugal. Sur la carte, de l'eau bleue. Maman dit : ça, c'est un paysage. C'est la mer. Tessa dit : la mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'huile chaude sent le citron dans la cuisine. Une poêle fait un petit chant gras. La fenêtre est ouverte sur la cour. Une sardine dessinée attend près du pain. Chouchou vit ici, avec maman. Tu as vu la boîte, Chouchou ? Il y a un poisson. Une sardine. Dessinée, sur le Portugal. En ce moment, Chouchou prend la boîte. Le métal est froid, un peu huileux. Derrière le poisson, c'est bleu. C'est la mer du Portugal. Le Portugal. Et la mer. Un pays. Un paysage. Chouchou veut poser l'image près d'elle. Pour voir la mer, en mangeant. Tu la mets contre le sel ? Oui. La poêle crache une goutte. La goutte d'huile tombe sur le coin. Oh. Le bleu est taché ! On essuie tout de suite ? Oui, maman. Maman tend un torchon sec. Chouchou tamponne le coin, tout doux. L'huile fait un rond brillant. Ça part ? Encore un peu. Le torchon sent le citron, maintenant. Le rond devient plus pâle. La sardine est encore là. Et la mer, derrière ? Elle revient. Tu tamponnes bien. Une miette de pain roule près de la boîte. Chouchou la pousse du doigt.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tessa s'assoit près de maman. Elles ouvrent une boîte de cartes.
-maman|On nomme un pays.
-narrateur|Tessa lit le nom : le Portugal. Elle répète : le Portugal. Sur la carte, de l'eau bleue.
-maman|Ça, c'est un paysage. C'est la mer.
-enfant-f|La mer. Autre carte : des sommets.
-narrateur|Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'huile chaude sent le citron dans la cuisine.
+narrateur|Une poêle fait un petit chant gras.
+narrateur|La fenêtre est ouverte sur la cour.
+narrateur|Une sardine dessinée attend près du pain.
+narrateur|Chouchou vit ici, avec maman.
+maman|Tu as vu la boîte, Chouchou ?
+enfant-f|Il y a un poisson.
+maman|Une sardine.
+maman|Dessinée, sur le Portugal.
+narrateur|En ce moment, Chouchou prend la boîte.
+narrateur|Le métal est froid, un peu huileux.
+enfant-f|Derrière le poisson, c'est bleu.
+maman|C'est la mer du Portugal.
+enfant-f|Le Portugal.
+enfant-f|Et la mer.
+maman|Un pays.
+maman|Un paysage.
+narrateur|Chouchou veut poser l'image près d'elle.
+enfant-f|Pour voir la mer, en mangeant.
+maman|Tu la mets contre le sel ?
+enfant-f|Oui.
+narrateur|La poêle crache une goutte.
+narrateur|La goutte d'huile tombe sur le coin.
+enfant-f|Oh.
+enfant-f|Le bleu est taché !
+maman|On essuie tout de suite ?
+enfant-f|Oui, maman.
+narrateur|Maman tend un torchon sec.
+narrateur|Chouchou tamponne le coin, tout doux.
+narrateur|L'huile fait un rond brillant.
+enfant-f|Ça part ?
+maman|Encore un peu.
+narrateur|Le torchon sent le citron, maintenant.
+narrateur|Le rond devient plus pâle.
+enfant-f|La sardine est encore là.
+maman|Et la mer, derrière ?
+enfant-f|Elle revient.
+maman|Tu tamponnes bien.
+narrateur|Une miette de pain roule près de la boîte.
+narrateur|Chouchou la pousse du doigt.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1390,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tessa nomme le Portugal. Elle nomme aussi quoi ?</t>
+          <t>Chouchou nomme le Portugal. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tessa &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me le Portugal. Elle nomme aussi quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou nomme le Portugal. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1410,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la mer | un paysage | un pays | le Portugal</t>
+          <t>mer | la mer | mer du Portugal | bleu | paysage</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a de l'eau bleue. C'est quel paysage ?</t>
+          <t>Chouchou nomme aussi la mer. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1474,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1550,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tessa nomme le Portugal. Elle nomme aussi quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou nomme le Portugal.
+narrateur|Elle nomme aussi quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1578,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tessa a dit le nom. Le Portugal. Elle a dit le paysage. La mer. La montagne aussi.</t>
+          <t>La mer. Oui, la mer du Portugal. Le coin de la boîte est presque sec. Le bleu a repris sa place. Merci, Chouchou. Tu as sauvé l'image. Je la mets ici. Chouchou pose la boîte contre le sel. La sardine dessinée regarde la poêle. On voit la mer, en cuisinant. Oui. La poêle chante moins fort. Maman coupe le citron en deux. Ça pique le nez. Comme au Portugal, presque. Une goutte de citron tombe dans l'huile. Ça sent plus fort, tout à coup. La mer, et le citron. Et la sardine.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tessa a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;. Le Portugal. Elle a dit le paysage. La mer. La montagne aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La mer. Oui, la mer du Portugal. Le coin de la boîte est presque sec. Le bleu a repris sa place. Merci, Chouchou. Tu as sauvé l'image. Je la mets ici. Chouchou pose la boîte contre le sel. La sardine dessinée regarde la poêle. On voit la mer, en cuisinant. Oui. La poêle chante moins fort. Maman coupe le citron en deux. Ça pique le nez. Comme au Portugal, presque. Une goutte de citron tombe dans l'huile. Ça sent plus fort, tout à coup. La mer, et le citron. Et la sardine.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1601,7 +1646,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1677,10 +1722,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tessa a dit le nom. Le Portugal. Elle a dit le paysage. La mer. La montagne aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-f|La mer.
+maman|Oui, la mer du Portugal.
+narrateur|Le coin de la boîte est presque sec.
+narrateur|Le bleu a repris sa place.
+maman|Merci, Chouchou.
+maman|Tu as sauvé l'image.
+enfant-f|Je la mets ici.
+narrateur|Chouchou pose la boîte contre le sel.
+narrateur|La sardine dessinée regarde la poêle.
+maman|On voit la mer, en cuisinant.
+enfant-f|Oui.
+narrateur|La poêle chante moins fort.
+narrateur|Maman coupe le citron en deux.
+enfant-f|Ça pique le nez.
+maman|Comme au Portugal, presque.
+narrateur|Une goutte de citron tombe dans l'huile.
+narrateur|Ça sent plus fort, tout à coup.
+enfant-f|La mer, et le citron.
+maman|Et la sardine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,12 +1767,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tessa range les cartes. Maman ferme la boîte.</t>
+          <t>Tu as fini d'essuyer ? Oui, maman. Elles s'assoient près de la table. Le pain est tiède sous les doigts. Je regarde la boîte. Le Portugal. Et la mer. Chouchou mange une bouchée. Elle garde les yeux sur le bleu. Ça sent la cuisine. Et un peu le large, aussi. La fenêtre amène un air de cour.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tessa range les cartes. Maman ferme la boîte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu as fini d'essuyer ? Oui, maman. Elles s'assoient près de la table. Le pain est tiède sous les doigts. Je regarde la boîte. Le Portugal. Et la mer. Chouchou mange une bouchée. Elle garde les yeux sur le bleu. Ça sent la cuisine. Et un peu le large, aussi. La fenêtre amène un air de cour.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1773,7 +1835,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1841,10 +1903,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Tessa range les cartes. Maman ferme la boîte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|Tu as fini d'essuyer ?
+enfant-f|Oui, maman.
+narrateur|Elles s'assoient près de la table.
+narrateur|Le pain est tiède sous les doigts.
+enfant-f|Je regarde la boîte.
+maman|Le Portugal.
+maman|Et la mer.
+narrateur|Chouchou mange une bouchée.
+narrateur|Elle garde les yeux sur le bleu.
+enfant-f|Ça sent la cuisine.
+maman|Et un peu le large, aussi.
+narrateur|La fenêtre amène un air de cour.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La boîte reste contre le sel. Le torchon sent encore le citron. La sardine garde la mer. Pour demain, aussi. L'huile chaude se tait, enfin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La boîte reste contre le sel. Le torchon sent encore le citron. La sardine garde la mer. Pour demain, aussi. L'huile chaude se tait, enfin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1930,14 +2002,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2009,10 +2081,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La boîte reste contre le sel.
+narrateur|Le torchon sent encore le citron.
+enfant-f|La sardine garde la mer.
+maman|Pour demain, aussi.
+narrateur|L'huile chaude se tait, enfin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>cuisine, huile de citron et boîte illustrée</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tessa, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
